--- a/65_Threshold_OUTPUT/reverse_Q4UZF6_Xanthomonas_campestris_pv__campestris_str__8004.xlsx
+++ b/65_Threshold_OUTPUT/reverse_Q4UZF6_Xanthomonas_campestris_pv__campestris_str__8004.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,15 +446,25 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>full_pattern</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>group1</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>group2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>full_pattern_html</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
@@ -477,15 +487,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>GGTGCGCTTCACCGCACC</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>GGTGCG</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>CGCACC</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;CTTCAC&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>0.01239504198320672</v>
       </c>
     </row>
@@ -506,15 +526,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>CGGTGCGCTTCACCG</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>CGGTG</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>CACCG</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;CGCTT&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>0.08256697321071571</v>
       </c>
     </row>
@@ -535,15 +565,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>ACGGT</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>GT</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;G&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -564,15 +604,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>CGGTGCG</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>CG</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>CG</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;GTG&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -593,15 +643,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>GCGC</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>GC</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>GC</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -622,15 +682,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>AACGGTGCGCTT</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;CGGTGCGC&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -651,15 +721,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>GCTTCACCGC</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>GC</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>GC</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;TTCACC&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -680,15 +760,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>GGTGCGCTTCACCGCACCC</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>GG</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>CC</t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;TGCGCTTCACCGCAC&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
